--- a/AAII_Financials/Quarterly/SWDBY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SWDBY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="493" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="516" uniqueCount="92">
   <si>
     <t>SWDBY</t>
   </si>
@@ -656,149 +656,152 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="42" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="43" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42916</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42825</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -841,86 +844,89 @@
       <c r="P8" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="Q8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R8" s="3">
         <v>1708000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1133900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>821100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>718800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>715000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>705600</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>695500</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>721300</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>765500</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>809700</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>891200</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>970900</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>991900</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>1070800</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>1046000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>1030400</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>998100</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>921300</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>879800</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>845400</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>867700</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>874100</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>871500</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>897900</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>857200</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>889700</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -1041,8 +1047,11 @@
       <c r="AP9" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AQ9" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1163,8 +1172,11 @@
       <c r="AP10" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AQ10" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1207,8 +1219,9 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1329,8 +1342,11 @@
       <c r="AP12" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AQ12" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1451,8 +1467,11 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1495,8 +1514,8 @@
       <c r="P14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
+      <c r="Q14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R14" s="3">
         <v>0</v>
@@ -1573,8 +1592,11 @@
       <c r="AP14" s="3">
         <v>0</v>
       </c>
+      <c r="AQ14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1617,86 +1639,89 @@
       <c r="P15" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="Q15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R15" s="3">
         <v>-86400</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>-80700</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>-41000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>-77800</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>-37500</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>-38100</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>-38800</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>-38000</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>-38400</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>-39000</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>-39700</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>-43000</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>-44600</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>-46400</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>-45500</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>-45000</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>-19500</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>-18500</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>-17900</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>-17500</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>-18400</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AM15" s="3">
         <v>-16500</v>
       </c>
-      <c r="AM15" s="3">
+      <c r="AN15" s="3">
         <v>-15200</v>
       </c>
-      <c r="AN15" s="3">
+      <c r="AO15" s="3">
         <v>-15300</v>
       </c>
-      <c r="AO15" s="3">
+      <c r="AP15" s="3">
         <v>-17400</v>
       </c>
-      <c r="AP15" s="3">
+      <c r="AQ15" s="3">
         <v>-19000</v>
       </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1736,8 +1761,9 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1780,86 +1806,89 @@
       <c r="P17" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="Q17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R17" s="3">
         <v>705000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>385500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>137000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>95600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>92700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>64000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>64500</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>104400</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>194600</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>189700</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>310800</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>470300</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>375700</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>295900</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>295200</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>299900</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>318200</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>268600</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>213800</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>204400</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>220200</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>231200</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>259000</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>258600</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>243400</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>249900</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1902,86 +1931,89 @@
       <c r="P18" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="Q18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R18" s="3">
         <v>1002900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>748400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>684100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>623300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>622300</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>641700</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>631000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>616900</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>570900</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>619900</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>580400</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>500600</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>616300</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>774900</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>750800</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>730500</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>679900</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>652700</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>666000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>640900</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>647500</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>642900</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>612500</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>639300</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>613800</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>639800</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2024,8 +2056,9 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -2068,86 +2101,89 @@
       <c r="P20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="Q20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R20" s="3">
         <v>-166100</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-71500</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-141000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-95300</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-76600</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>3700</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>7500</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-32300</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-36800</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>12600</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>35600</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-642900</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-2200</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-67600</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>6200</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>49800</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-30300</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>79200</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>94700</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>23100</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-25200</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>23700</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>36200</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>76600</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>-30200</v>
       </c>
-      <c r="AP20" s="3">
+      <c r="AQ20" s="3">
         <v>45200</v>
       </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -2190,33 +2226,33 @@
       <c r="P21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="Q21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R21" s="3">
         <v>835500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>676300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>544300</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>566900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>543200</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>644000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>639800</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>622600</v>
       </c>
-      <c r="Y21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Z21" s="3" t="s">
         <v>5</v>
       </c>
@@ -2229,47 +2265,50 @@
       <c r="AC21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AD21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE21" s="3">
         <v>706000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>758400</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>825300</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>648900</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>732300</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>761100</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>681500</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>624200</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>667900</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>649300</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>731300</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>582000</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>686300</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2312,8 +2351,8 @@
       <c r="P22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
+      <c r="Q22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R22" s="3">
         <v>0</v>
@@ -2390,8 +2429,11 @@
       <c r="AP22" s="3">
         <v>0</v>
       </c>
+      <c r="AQ22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -2434,86 +2476,89 @@
       <c r="P23" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="Q23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R23" s="3">
         <v>836800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>676900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>543200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>528000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>545700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>645400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>638500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>584600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>534100</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>632500</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>616100</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-142300</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>614100</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>707300</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>757000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>780300</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>649600</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>731800</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>760700</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>664000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>622300</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>666600</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>648600</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>716000</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>583600</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>685000</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2556,86 +2601,89 @@
       <c r="P24" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="Q24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R24" s="3">
         <v>171900</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>137300</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>107300</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>104600</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>104000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>124200</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>120000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>114200</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>108100</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>113800</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>118500</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>43900</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>110600</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>142400</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>139800</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>159200</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>122300</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>150400</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>135100</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>140800</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>112200</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>155400</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>137300</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>134100</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>113100</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>137900</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2756,8 +2804,11 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2800,86 +2851,89 @@
       <c r="P26" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="Q26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R26" s="3">
         <v>664900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>539600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>435900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>423400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>441600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>521200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>518500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>470300</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>426000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>518700</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>497500</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-186200</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>503500</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>564900</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>617200</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>621100</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>527300</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>581400</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>625600</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>523200</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>510100</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>511200</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>511300</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>581900</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>470500</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>547100</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2922,86 +2976,89 @@
       <c r="P27" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="Q27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R27" s="3">
         <v>665000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>539200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>435900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>423400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>441600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>521100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>518400</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>470400</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>426000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>518600</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>497600</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-186200</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>503500</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>564600</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>616500</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>620600</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>526900</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>580800</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>625000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>523100</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>509900</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>510500</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>510900</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>581700</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>470200</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>546700</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3122,8 +3179,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3166,8 +3226,8 @@
       <c r="P29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q29" s="3">
-        <v>0</v>
+      <c r="Q29" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R29" s="3">
         <v>0</v>
@@ -3226,8 +3286,8 @@
       <c r="AJ29" s="3">
         <v>0</v>
       </c>
-      <c r="AK29" s="3" t="s">
-        <v>5</v>
+      <c r="AK29" s="3">
+        <v>0</v>
       </c>
       <c r="AL29" s="3" t="s">
         <v>5</v>
@@ -3238,14 +3298,17 @@
       <c r="AN29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AO29" s="3">
-        <v>0</v>
+      <c r="AO29" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AP29" s="3">
         <v>0</v>
       </c>
+      <c r="AQ29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3366,8 +3429,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3488,8 +3554,11 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3532,86 +3601,89 @@
       <c r="P32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="Q32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R32" s="3">
         <v>166100</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>71500</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>141000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>95300</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>76600</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-3700</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-7500</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>32300</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>36800</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-12600</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-35600</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>642900</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>2200</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>67600</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-6200</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-49800</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>30300</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-79200</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-94700</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-23100</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>25200</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-23700</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>-36200</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>-76600</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>30200</v>
       </c>
-      <c r="AP32" s="3">
+      <c r="AQ32" s="3">
         <v>-45200</v>
       </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -3654,86 +3726,89 @@
       <c r="P33" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="Q33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R33" s="3">
         <v>665000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>539200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>435900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>423400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>441600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>521100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>518400</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>470400</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>426000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>518600</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>497600</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-186200</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>503500</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>564600</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>616500</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>620600</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>526900</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>580800</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>625000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>523100</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>509900</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>510500</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>510900</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>581700</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>470200</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>546700</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3854,8 +3929,11 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -3898,213 +3976,219 @@
       <c r="P35" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="Q35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R35" s="3">
         <v>665000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>539200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>435900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>423400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>441600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>521100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>518400</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>470400</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>426000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>518600</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>497600</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-186200</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>503500</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>564600</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>616500</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>620600</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>526900</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>580800</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>625000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>523100</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>509900</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>510500</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>510900</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>581700</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>470200</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>546700</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42916</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42825</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4147,8 +4231,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4191,297 +4276,304 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>26953300</v>
+      </c>
+      <c r="E41" s="3">
         <v>29332400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>28601600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>34050300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>34178900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>36184500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>29420300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>27741700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>29897900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>32438200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>25156800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>26427500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>33222600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>34894000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>41390300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>49996700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>46887200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>45581800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>36378300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>65378000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>59312200</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>48146000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>30917800</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>39163500</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>40056700</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>38011500</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>26849700</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>29678400</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>32618300</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>32501600</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>22441800</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>35202400</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>49244900</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>44922100</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>24467100</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>40233200</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>50311700</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>50380500</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>17333600</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>39220600</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>4161600</v>
+      </c>
+      <c r="E42" s="3">
         <v>3964500</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>14603200</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>1825500</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>2736600</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>2538500</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>11611900</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>2138000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>1704700</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>3209800</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>8281100</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>2905200</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>3351600</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>1927700</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>46414800</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>53939200</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>61680100</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>61267000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>50860300</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>50263500</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>48179000</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>61950600</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>47036700</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>64040800</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>74073200</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>56696400</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>52068000</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>61109000</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>54002700</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>56123200</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>41498700</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>35274800</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>35029100</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>30036800</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>37840900</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AM42" s="3">
         <v>31885600</v>
       </c>
-      <c r="AM42" s="3">
+      <c r="AN42" s="3">
         <v>32621900</v>
       </c>
-      <c r="AN42" s="3">
+      <c r="AO42" s="3">
         <v>35850000</v>
       </c>
-      <c r="AO42" s="3">
+      <c r="AP42" s="3">
         <v>46163500</v>
       </c>
-      <c r="AP42" s="3">
+      <c r="AQ42" s="3">
         <v>38765200</v>
       </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E43" s="3">
+      <c r="E43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F43" s="3">
         <v>351400</v>
       </c>
-      <c r="F43" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="G43" s="3" t="s">
         <v>5</v>
       </c>
       <c r="H43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I43" s="3">
+      <c r="I43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J43" s="3">
         <v>268800</v>
       </c>
-      <c r="J43" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K43" s="3" t="s">
         <v>5</v>
       </c>
       <c r="L43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M43" s="3">
+      <c r="M43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N43" s="3">
         <v>239600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>147600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>149800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>155300</v>
       </c>
-      <c r="Q43" s="3">
-        <v>0</v>
-      </c>
       <c r="R43" s="3">
         <v>0</v>
       </c>
@@ -4557,52 +4649,55 @@
       <c r="AP43" s="3">
         <v>0</v>
       </c>
+      <c r="AQ43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E44" s="3">
+      <c r="E44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F44" s="3">
         <v>2500</v>
       </c>
-      <c r="F44" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="G44" s="3" t="s">
         <v>5</v>
       </c>
       <c r="H44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I44" s="3">
+      <c r="I44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J44" s="3">
         <v>3100</v>
       </c>
-      <c r="J44" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K44" s="3" t="s">
         <v>5</v>
       </c>
       <c r="L44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M44" s="3">
+      <c r="M44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N44" s="3">
         <v>2900</v>
       </c>
-      <c r="N44" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O44" s="3" t="s">
         <v>5</v>
       </c>
       <c r="P44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q44" s="3">
-        <v>0</v>
+      <c r="Q44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R44" s="3">
         <v>0</v>
@@ -4679,52 +4774,55 @@
       <c r="AP44" s="3">
         <v>0</v>
       </c>
+      <c r="AQ44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>753900</v>
+      </c>
+      <c r="E45" s="3">
         <v>778200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>108600</v>
       </c>
-      <c r="F45" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="G45" s="3" t="s">
         <v>5</v>
       </c>
       <c r="H45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I45" s="3">
+      <c r="I45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J45" s="3">
         <v>79100</v>
       </c>
-      <c r="J45" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K45" s="3" t="s">
         <v>5</v>
       </c>
       <c r="L45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M45" s="3">
+      <c r="M45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N45" s="3">
         <v>80700</v>
       </c>
-      <c r="N45" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O45" s="3" t="s">
         <v>5</v>
       </c>
       <c r="P45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q45" s="3">
-        <v>0</v>
+      <c r="Q45" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R45" s="3">
         <v>0</v>
@@ -4801,53 +4899,56 @@
       <c r="AP45" s="3">
         <v>0</v>
       </c>
+      <c r="AQ45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>31868800</v>
+      </c>
+      <c r="E46" s="3">
         <v>34075000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>45625100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>35875700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>36915500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>38723000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>42864600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>29879600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>31602600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>35648000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>38182400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>29690800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>36964800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>37240800</v>
       </c>
-      <c r="Q46" s="3">
-        <v>0</v>
-      </c>
       <c r="R46" s="3">
         <v>0</v>
       </c>
@@ -4923,374 +5024,386 @@
       <c r="AP46" s="3">
         <v>0</v>
       </c>
+      <c r="AQ46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>88194300</v>
+      </c>
+      <c r="E47" s="3">
         <v>79690900</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>74956500</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>77632300</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>72267400</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>66583200</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>60917200</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>78900600</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>68625000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>65337400</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>59049800</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>66949200</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>63153200</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>67242200</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>766900</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>734400</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>697000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>744900</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>703800</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>713700</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>680600</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>715900</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>688300</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>702500</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>711900</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>754300</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>759400</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>777800</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>690200</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>730300</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>698800</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>707200</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>664400</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>662700</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>684300</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>799000</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>776200</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>824700</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <v>830900</v>
       </c>
-      <c r="AP47" s="3">
+      <c r="AQ47" s="3">
         <v>820500</v>
       </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E48" s="3">
+      <c r="E48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F48" s="3">
         <v>555200</v>
       </c>
-      <c r="F48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="G48" s="3" t="s">
         <v>5</v>
       </c>
       <c r="H48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I48" s="3">
+      <c r="I48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J48" s="3">
         <v>390800</v>
       </c>
-      <c r="J48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K48" s="3" t="s">
         <v>5</v>
       </c>
       <c r="L48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M48" s="3">
+      <c r="M48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N48" s="3">
         <v>470500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>499700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>526300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>533900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>533700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>498900</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>506000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>505900</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>504500</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>493600</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>501000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>510400</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>512100</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>549600</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>586100</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>625500</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>633500</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>679300</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>671300</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>697400</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>225700</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>200100</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>205600</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>205900</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>210400</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>212100</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>201000</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>209400</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>211600</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>218900</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>2390200</v>
+      </c>
+      <c r="E49" s="3">
         <v>2410100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>2458500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>2225300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>2200700</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>2036400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1885800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>2085900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1977700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1960500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>2032500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1918200</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1945800</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1960400</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>3332300</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>2523000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>2555700</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>2444600</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>1780000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>1807200</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>1755300</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>1777200</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>1734400</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>1821800</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>1877200</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>2054200</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>2031100</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>2170800</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>2045500</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>2048600</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>1965000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>1781300</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>1761900</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>1759600</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>1757700</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>1718000</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>1592500</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>1630900</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>1621000</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>1622500</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5411,8 +5524,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5533,130 +5649,136 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>4851500</v>
+      </c>
+      <c r="E52" s="3">
         <v>4547000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>2214500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>5191500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>7185400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>4904400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>1092000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>3910200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>3902700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>4100200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1001400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1673900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>2373100</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>2992000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>253700</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>308400</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>98500</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>12200</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>10300</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>14700</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>14500</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>16600</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>11700</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>19700</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>20700</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>19900</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>19300</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>20800</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>21100</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>19900</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>18800</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>18000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>18100</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>18800</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>18600</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>17300</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>16700</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>21200</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>18200</v>
       </c>
-      <c r="AP52" s="3">
+      <c r="AQ52" s="3">
         <v>20800</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5777,130 +5899,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>341176900</v>
+      </c>
+      <c r="E54" s="3">
         <v>334952000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>332288000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>331648800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>329405800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>308765700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>271944300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>309006400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>289454800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>288006900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>283942500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>276975500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>282753000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>293212000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>279612600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>288938200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>281717100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>272427900</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>251241400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>287198300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>273920400</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>267563900</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>245089900</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>265720100</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>283979100</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>295318300</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>273815500</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>303514700</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>286545400</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>289967600</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>257828900</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>258770100</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>275002200</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>256616400</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>238168100</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>264780900</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>261147700</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>282515500</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>244545100</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>271737700</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5943,8 +6071,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5987,53 +6116,54 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>139220700</v>
+      </c>
+      <c r="E57" s="3">
         <v>138242100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>141055000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>138657600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>138200200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>128111100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>116068400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>125482900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>120970900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>118402800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>122349200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>117247100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>120287000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>125833600</v>
       </c>
-      <c r="Q57" s="3">
-        <v>0</v>
-      </c>
       <c r="R57" s="3">
         <v>0</v>
       </c>
@@ -6109,92 +6239,95 @@
       <c r="AP57" s="3">
         <v>0</v>
       </c>
+      <c r="AQ57" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>39766000</v>
+      </c>
+      <c r="E58" s="3">
         <v>41298800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>36634800</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>45396400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>36803000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>35588700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>33970300</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>43384600</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>34798700</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>37464700</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>42390000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>41267800</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>39665900</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>47311600</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>43394200</v>
       </c>
-      <c r="R58" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S58" s="3" t="s">
         <v>5</v>
       </c>
       <c r="T58" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U58" s="3">
+      <c r="U58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V58" s="3">
         <v>30241800</v>
       </c>
-      <c r="V58" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W58" s="3" t="s">
         <v>5</v>
       </c>
       <c r="X58" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Y58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z58" s="3">
         <v>25909200</v>
       </c>
-      <c r="Z58" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AA58" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AB58" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AC58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD58" s="3">
         <v>34291700</v>
       </c>
-      <c r="AD58" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AE58" s="3" t="s">
         <v>5</v>
       </c>
@@ -6207,8 +6340,8 @@
       <c r="AH58" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AI58" s="3">
-        <v>0</v>
+      <c r="AI58" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AJ58" s="3">
         <v>0</v>
@@ -6231,175 +6364,181 @@
       <c r="AP58" s="3">
         <v>0</v>
       </c>
+      <c r="AQ58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>3947100</v>
+      </c>
+      <c r="E59" s="3">
         <v>4068800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>18085200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>2839000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>3063400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>2390800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>12858500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>4142700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2968200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>3170800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>12558800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>2545100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>3201600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>3078700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>633500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>565800</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>555100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>614500</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>501000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>510600</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>507600</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>549200</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>421500</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>454800</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>452700</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>1048400</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>593400</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>577800</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>527000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>657100</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>593800</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>473300</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>508700</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>512400</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>1251900</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>1096400</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>1158400</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>1724000</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>1351900</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>1471000</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>182933800</v>
+      </c>
+      <c r="E60" s="3">
         <v>183609800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>196165000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>186893000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>178066600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>166090600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>163202100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>173010200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>158737800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>159038300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>177637100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>161600100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>163680100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>176807800</v>
       </c>
-      <c r="Q60" s="3">
-        <v>0</v>
-      </c>
       <c r="R60" s="3">
         <v>0</v>
       </c>
@@ -6475,252 +6614,261 @@
       <c r="AP60" s="3">
         <v>0</v>
       </c>
+      <c r="AQ60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>77083700</v>
+      </c>
+      <c r="E61" s="3">
         <v>76646000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>71574500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>69241700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>79790900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>75090100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>58212300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>69262500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>69165500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>67855600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>58634900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>63675100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>66714300</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>64555300</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>42454200</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>54524800</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>55197000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>59602100</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>43509900</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>56500800</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>57951700</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>59532300</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>48093600</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>68257400</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>73981600</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>84042000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>67869000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>95392200</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>108811600</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>111467000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>96256500</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>100491900</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>109887800</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>96556100</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>93615800</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>101427100</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>99439800</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>113849200</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>98640600</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>86939400</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>59794600</v>
+      </c>
+      <c r="E62" s="3">
         <v>53773900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>38819100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>52403700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>49601400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>47618700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>29883900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>46141100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>42715300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>43142400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>27121000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>33567600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>34827600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>34740400</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>2807100</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>2798200</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>2746800</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>2844900</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>654800</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>691700</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>633500</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>667500</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>784800</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>913300</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>1028200</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>1003800</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>1394300</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>1592500</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>1438400</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>1086100</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>970200</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>780400</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>763700</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>717000</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>776700</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>728800</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>677200</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>674000</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>643000</v>
       </c>
-      <c r="AP62" s="3">
+      <c r="AQ62" s="3">
         <v>814800</v>
       </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6841,8 +6989,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6963,8 +7114,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7085,130 +7239,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>319812100</v>
+      </c>
+      <c r="E66" s="3">
         <v>314029700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>307787600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>308538400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>307458900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>288799300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>252165200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>288413800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>270618600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>270036400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>264175600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>259267700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>265636900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>276470800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>262368400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>272606500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>266071400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>257799600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>236474400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>271596400</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>259068900</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>253026000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>230432700</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>250879000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>269148400</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>279696100</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>258055800</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>287319600</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>271594200</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>275084700</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>242057200</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>244717600</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>261692000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>243880300</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>223812000</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>250910000</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>247801800</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>268957400</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>229842600</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>257661300</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7251,8 +7411,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7373,8 +7534,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7495,8 +7659,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7617,8 +7784,11 @@
       <c r="AP70" s="3">
         <v>0</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7739,130 +7909,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>16661700</v>
+      </c>
+      <c r="E72" s="3">
         <v>16158100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>19617700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>18278600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>17137500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>15468300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>15569500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>16037200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>14466500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>13601800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>15210100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>13418800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>12737400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>12275700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>12718200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>11948900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>11280300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>10433100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>10718300</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>11426500</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>10756500</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>10360400</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>10903800</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>10432600</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>10250400</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>10588400</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>11156700</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>10740700</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>9775400</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>9646400</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>11161800</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>9388500</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>8675100</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>8125500</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>10106000</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>9223500</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>8705700</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>8678600</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>9808800</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>9164500</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7983,8 +8159,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8105,8 +8284,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8227,130 +8409,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>21362300</v>
+      </c>
+      <c r="E76" s="3">
         <v>20919800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>24497800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>23108100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>21944800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>19963900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>19776600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>20589500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>18833300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>17967700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>19764000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>17705000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>17113600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>16738400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>17244200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>16331700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>15645700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>14628200</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>14766900</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>15601900</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>14851500</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>14537800</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>14657200</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>14841100</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>14830700</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>15622200</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>15759700</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>16195200</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>14951200</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>14883000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>15771700</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>14052500</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>13310200</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>12736100</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>14356200</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>13870900</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>13345900</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>13558100</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>14702500</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>14076400</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8471,135 +8659,141 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42916</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42825</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -8642,86 +8836,89 @@
       <c r="P81" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="Q81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R81" s="3">
         <v>665000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>539200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>435900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>423400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>441600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>521100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>518400</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>470400</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>426000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>518600</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>497600</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-186200</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>503500</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>564600</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>616500</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>620600</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>526900</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>580800</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>625000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>523100</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>509900</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>510500</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>510900</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>581700</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>470200</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>546700</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8764,53 +8961,54 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>34400</v>
+      </c>
+      <c r="E83" s="3">
         <v>33000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>-15500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>32500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>13100</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>48100</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>-5100</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>29800</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>17100</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>43300</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>4600</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>28300</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>16800</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>44100</v>
       </c>
-      <c r="Q83" s="3">
-        <v>0</v>
-      </c>
       <c r="R83" s="3">
         <v>0</v>
       </c>
@@ -8886,8 +9084,11 @@
       <c r="AP83" s="3">
         <v>0</v>
       </c>
+      <c r="AQ83" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9008,8 +9209,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9130,8 +9334,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9252,8 +9459,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9374,8 +9584,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9496,130 +9709,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-420100</v>
+      </c>
+      <c r="E89" s="3">
         <v>3836600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-8664100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-620800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-1837600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>3537300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>385700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-2671000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-934100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>6749600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>4245300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-7074200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-1743500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-1925900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-9039600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1082200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>19900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>5877600</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-26013200</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>4660600</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>8020400</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>18814200</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-12773500</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>5130000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>9195600</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>11357000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>6563200</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-3438100</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>3675100</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-2728600</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-1879800</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>-5103800</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>-8245800</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>17813800</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>-6811800</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>-13678900</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>9731800</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>17970200</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>-8620600</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>-9188900</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9662,130 +9881,134 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-11100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-12200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-14000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-12700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-19600</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-5500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-12600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-7500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-15300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-2800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-19700</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-19600</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-8200</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-34000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-120000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-109000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-76000</v>
-      </c>
-      <c r="T91" s="3">
-        <v>-58000</v>
       </c>
       <c r="U91" s="3">
         <v>-58000</v>
       </c>
       <c r="V91" s="3">
+        <v>-58000</v>
+      </c>
+      <c r="W91" s="3">
         <v>-61000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-7500</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-5100</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-5200</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-3900</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-20900</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-7300</v>
       </c>
-      <c r="AC91" s="3">
-        <v>0</v>
-      </c>
       <c r="AD91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE91" s="3">
         <v>-4500</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>463400</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-494400</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-763500</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-299000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-342300</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-263200</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>1700</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-14600</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-29400</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-12600</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-9200</v>
       </c>
-      <c r="AP91" s="3" t="s">
+      <c r="AQ91" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9906,8 +10129,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10028,130 +10254,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-12200</v>
+      </c>
+      <c r="E94" s="3">
         <v>-100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-346300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-47800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-14200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>10600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-9100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-4900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-6700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>7000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>5800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-18400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-26500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-5900</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-8500</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>78800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>2400</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>15700</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-800</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>40100</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>3200</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>67800</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>58500</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-2400</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>10500</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>25200</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>1700</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>79700</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>8100</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>77000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>97200</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>18900</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-11100</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>157400</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-137000</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-4200</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>67800</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-25900</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>28500</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10194,52 +10426,53 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>0</v>
+      </c>
+      <c r="E96" s="3">
         <v>3518700</v>
       </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
       <c r="F96" s="3">
         <v>0</v>
       </c>
       <c r="G96" s="3">
+        <v>0</v>
+      </c>
+      <c r="H96" s="3">
         <v>2565000</v>
       </c>
-      <c r="H96" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
+      <c r="I96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="J96" s="3">
         <v>0</v>
       </c>
       <c r="K96" s="3">
+        <v>0</v>
+      </c>
+      <c r="L96" s="3">
         <v>1608500</v>
       </c>
-      <c r="L96" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
       </c>
       <c r="O96" s="3">
+        <v>0</v>
+      </c>
+      <c r="P96" s="3">
         <v>1016300</v>
       </c>
-      <c r="P96" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q96" s="3">
-        <v>0</v>
+      <c r="Q96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R96" s="3">
         <v>0</v>
@@ -10251,20 +10484,20 @@
         <v>0</v>
       </c>
       <c r="U96" s="3">
+        <v>0</v>
+      </c>
+      <c r="V96" s="3">
         <v>-747700</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-308300</v>
       </c>
-      <c r="W96" s="3">
-        <v>0</v>
-      </c>
       <c r="X96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y96" s="3">
         <v>-460600</v>
       </c>
-      <c r="Y96" s="3">
-        <v>0</v>
-      </c>
       <c r="Z96" s="3">
         <v>0</v>
       </c>
@@ -10281,11 +10514,11 @@
         <v>0</v>
       </c>
       <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF96" s="3">
         <v>-1836300</v>
       </c>
-      <c r="AF96" s="3">
-        <v>0</v>
-      </c>
       <c r="AG96" s="3">
         <v>0</v>
       </c>
@@ -10293,31 +10526,34 @@
         <v>0</v>
       </c>
       <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ96" s="3">
         <v>-500</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-1508800</v>
       </c>
-      <c r="AK96" s="3">
-        <v>0</v>
-      </c>
       <c r="AL96" s="3">
         <v>0</v>
       </c>
       <c r="AM96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN96" s="3">
         <v>-400</v>
       </c>
-      <c r="AN96" s="3">
+      <c r="AO96" s="3">
         <v>-1668200</v>
       </c>
-      <c r="AO96" s="3">
-        <v>0</v>
-      </c>
       <c r="AP96" s="3">
         <v>0</v>
       </c>
+      <c r="AQ96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10438,8 +10674,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10560,8 +10799,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10682,370 +10924,382 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-1557100</v>
+      </c>
+      <c r="E100" s="3">
         <v>-2389400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>3186000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>325300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-2530800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>1149900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>3431300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-778000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1692900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>1551000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-7107000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>842000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>844900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>1290200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-198700</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>1786300</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-1106600</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>469600</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-720600</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>296200</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>1329400</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>439600</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-59800</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-1049800</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-1860500</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>2284800</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-3637800</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-886900</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-2643700</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>11141700</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-13549800</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-9462700</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>11938100</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>2527200</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-7854800</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>3442300</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-7063300</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>14437800</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-7369300</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>-1577200</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>366200</v>
+      </c>
+      <c r="E101" s="3">
         <v>-951000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>189500</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-48400</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-192000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>468900</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-624600</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-211500</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>627600</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>213200</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>555000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>44200</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>527200</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>222200</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>566600</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>47400</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>522600</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>195900</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>72700</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>61900</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-157800</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>226800</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-394100</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>61400</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-482200</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>535000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-258300</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>144300</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>140000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>138600</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-37700</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-95800</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>118100</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>307900</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>45900</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>12500</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>52600</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>-14500</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AP101" s="3">
         <v>-38900</v>
       </c>
-      <c r="AP101" s="3">
+      <c r="AQ101" s="3">
         <v>137900</v>
       </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-1848600</v>
+      </c>
+      <c r="E102" s="3">
         <v>1630900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-6208000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-442600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-4016400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>3746700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>3997400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-3502400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-2825700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>8776600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-3480500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-6462100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-271200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-448900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-8677600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>2907400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-485300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>6545400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-26645300</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>5017900</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>9232100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>19483800</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-8943500</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>828800</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>8693500</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>11055200</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-1919500</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-4178900</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>1251200</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>8559900</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-15350100</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-14565000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>3798700</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>20632000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-14629600</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-10361100</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>2716900</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>32461300</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>-16054700</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>-10599700</v>
       </c>
     </row>
